--- a/new-stats/montevideo-city-torque.xlsx
+++ b/new-stats/montevideo-city-torque.xlsx
@@ -1969,22 +1969,58 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>21/09/2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Central Esp.</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Montevideo City</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>16</v>
+      </c>
+      <c r="N29" t="n">
+        <v>8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>10</v>
+      </c>
+      <c r="P29" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>

--- a/new-stats/montevideo-city-torque.xlsx
+++ b/new-stats/montevideo-city-torque.xlsx
@@ -2023,22 +2023,58 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>27/09/2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Montevideo City</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Maldonado</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>4</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>

--- a/new-stats/montevideo-city-torque.xlsx
+++ b/new-stats/montevideo-city-torque.xlsx
@@ -2077,22 +2077,58 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Montevideo City</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Penarol</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>11</v>
+      </c>
+      <c r="N31" t="n">
+        <v>4</v>
+      </c>
+      <c r="O31" t="n">
+        <v>4</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>

--- a/new-stats/montevideo-city-torque.xlsx
+++ b/new-stats/montevideo-city-torque.xlsx
@@ -2131,22 +2131,58 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Montevideo City</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>9</v>
+      </c>
+      <c r="N32" t="n">
+        <v>8</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2</v>
+      </c>
+      <c r="P32" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>

--- a/new-stats/montevideo-city-torque.xlsx
+++ b/new-stats/montevideo-city-torque.xlsx
@@ -2185,22 +2185,58 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>09/10/2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Montevideo City</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Danubio</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>11</v>
+      </c>
+      <c r="N33" t="n">
+        <v>8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>

--- a/new-stats/montevideo-city-torque.xlsx
+++ b/new-stats/montevideo-city-torque.xlsx
@@ -2239,22 +2239,58 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Albion</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Montevideo City</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2</v>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>17</v>
+      </c>
+      <c r="N34" t="n">
+        <v>10</v>
+      </c>
+      <c r="O34" t="n">
+        <v>9</v>
+      </c>
+      <c r="P34" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
